--- a/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
   <si>
     <t>Record</t>
   </si>
@@ -30,187 +30,172 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Mr Steinfeld's Stars</t>
+  </si>
+  <si>
     <t>Chicken Fried Chicken Meal</t>
   </si>
   <si>
+    <t>AJ's Awesome Team</t>
+  </si>
+  <si>
+    <t>I'm Batman</t>
+  </si>
+  <si>
+    <t>Division iPad</t>
+  </si>
+  <si>
+    <t>3rd World Immigrant</t>
+  </si>
+  <si>
+    <t>Griddy Little Liars</t>
+  </si>
+  <si>
+    <t>All my homies hate Dallas</t>
+  </si>
+  <si>
+    <t>Michael, The Baker</t>
+  </si>
+  <si>
     <t>Scrappy Dub</t>
   </si>
   <si>
-    <t>Mr Steinfeld's Stars</t>
-  </si>
-  <si>
-    <t>3rd World Immigrant</t>
-  </si>
-  <si>
-    <t>Michael, The Baker</t>
-  </si>
-  <si>
-    <t>Division iPad</t>
-  </si>
-  <si>
-    <t>All my homies hate Dallas</t>
-  </si>
-  <si>
-    <t>I'm Batman</t>
-  </si>
-  <si>
-    <t>Griddy Little Liars</t>
-  </si>
-  <si>
-    <t>AJ's Awesome Team</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>62.7%</t>
-  </si>
-  <si>
-    <t>61.5%</t>
+    <t>62.5%</t>
+  </si>
+  <si>
+    <t>61.8%</t>
+  </si>
+  <si>
+    <t>61.2%</t>
   </si>
   <si>
     <t>61.0%</t>
   </si>
   <si>
-    <t>60.8%</t>
-  </si>
-  <si>
-    <t>60.6%</t>
-  </si>
-  <si>
-    <t>59.7%</t>
-  </si>
-  <si>
-    <t>59.6%</t>
-  </si>
-  <si>
-    <t>58.5%</t>
-  </si>
-  <si>
-    <t>57.9%</t>
+    <t>60.7%</t>
+  </si>
+  <si>
+    <t>60.5%</t>
   </si>
   <si>
     <t>57.7%</t>
   </si>
   <si>
-    <t>-168</t>
-  </si>
-  <si>
-    <t>-160</t>
+    <t>56.8%</t>
+  </si>
+  <si>
+    <t>-167</t>
+  </si>
+  <si>
+    <t>-162</t>
+  </si>
+  <si>
+    <t>-158</t>
   </si>
   <si>
     <t>-156</t>
   </si>
   <si>
-    <t>-155</t>
-  </si>
-  <si>
     <t>-154</t>
   </si>
   <si>
-    <t>-148</t>
-  </si>
-  <si>
-    <t>-141</t>
-  </si>
-  <si>
-    <t>-138</t>
+    <t>-153</t>
   </si>
   <si>
     <t>-136</t>
   </si>
   <si>
+    <t>-131</t>
+  </si>
+  <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>12.2%</t>
-  </si>
-  <si>
-    <t>11.3%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
+    <t>11.0%</t>
+  </si>
+  <si>
+    <t>10.6%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>+793</t>
+  </si>
+  <si>
+    <t>+801</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>+1090</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
   </si>
   <si>
     <t>10.1%</t>
   </si>
   <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
     <t>9.7%</t>
   </si>
   <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>7.4%</t>
-  </si>
-  <si>
-    <t>+720</t>
-  </si>
-  <si>
-    <t>+785</t>
-  </si>
-  <si>
-    <t>+852</t>
+    <t>9.4%</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+871</t>
   </si>
   <si>
     <t>+890</t>
   </si>
   <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
     <t>+931</t>
   </si>
   <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+1251</t>
-  </si>
-  <si>
-    <t>11.5%</t>
-  </si>
-  <si>
-    <t>10.7%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>9.9%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
-  </si>
-  <si>
-    <t>+770</t>
-  </si>
-  <si>
-    <t>+835</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+910</t>
-  </si>
-  <si>
     <t>+964</t>
-  </si>
-  <si>
-    <t>+1076</t>
   </si>
 </sst>
 </file>
@@ -596,7 +581,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -610,7 +595,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -624,7 +609,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -638,7 +623,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -649,10 +634,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -663,10 +648,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -677,10 +662,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -691,10 +676,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -705,10 +690,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -719,10 +704,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -751,72 +736,72 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -827,24 +812,24 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -855,38 +840,38 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -907,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -915,44 +900,44 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -963,94 +948,94 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
   <si>
     <t>Record</t>
   </si>
@@ -30,172 +30,190 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Griddy Little Liars</t>
+  </si>
+  <si>
+    <t>All my homies hate Dallas</t>
+  </si>
+  <si>
+    <t>Chicken Fried Chicken Meal</t>
+  </si>
+  <si>
+    <t>Division iPad</t>
+  </si>
+  <si>
+    <t>AJ's Awesome Team</t>
+  </si>
+  <si>
     <t>Mr Steinfeld's Stars</t>
   </si>
   <si>
-    <t>Chicken Fried Chicken Meal</t>
-  </si>
-  <si>
-    <t>AJ's Awesome Team</t>
+    <t>Scrappy Dub</t>
+  </si>
+  <si>
+    <t>3rd World Immigrant</t>
+  </si>
+  <si>
+    <t>Michael, The Baker</t>
   </si>
   <si>
     <t>I'm Batman</t>
   </si>
   <si>
-    <t>Division iPad</t>
-  </si>
-  <si>
-    <t>3rd World Immigrant</t>
-  </si>
-  <si>
-    <t>Griddy Little Liars</t>
-  </si>
-  <si>
-    <t>All my homies hate Dallas</t>
-  </si>
-  <si>
-    <t>Michael, The Baker</t>
-  </si>
-  <si>
-    <t>Scrappy Dub</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
+    <t>62.9%</t>
+  </si>
+  <si>
     <t>62.5%</t>
   </si>
   <si>
-    <t>61.8%</t>
-  </si>
-  <si>
-    <t>61.2%</t>
-  </si>
-  <si>
-    <t>61.0%</t>
-  </si>
-  <si>
-    <t>60.7%</t>
-  </si>
-  <si>
-    <t>60.5%</t>
-  </si>
-  <si>
-    <t>57.7%</t>
-  </si>
-  <si>
-    <t>56.8%</t>
+    <t>62.3%</t>
+  </si>
+  <si>
+    <t>59.8%</t>
+  </si>
+  <si>
+    <t>59.4%</t>
+  </si>
+  <si>
+    <t>59.2%</t>
+  </si>
+  <si>
+    <t>59.1%</t>
+  </si>
+  <si>
+    <t>58.0%</t>
+  </si>
+  <si>
+    <t>57.0%</t>
+  </si>
+  <si>
+    <t>-170</t>
   </si>
   <si>
     <t>-167</t>
   </si>
   <si>
-    <t>-162</t>
-  </si>
-  <si>
-    <t>-158</t>
-  </si>
-  <si>
-    <t>-156</t>
-  </si>
-  <si>
-    <t>-154</t>
-  </si>
-  <si>
-    <t>-153</t>
-  </si>
-  <si>
-    <t>-136</t>
-  </si>
-  <si>
-    <t>-131</t>
+    <t>-165</t>
+  </si>
+  <si>
+    <t>-149</t>
+  </si>
+  <si>
+    <t>-146</t>
+  </si>
+  <si>
+    <t>-145</t>
+  </si>
+  <si>
+    <t>-144</t>
+  </si>
+  <si>
+    <t>-138</t>
+  </si>
+  <si>
+    <t>-133</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>11.1%</t>
+    <t>11.3%</t>
   </si>
   <si>
     <t>11.0%</t>
   </si>
   <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>+785</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+953</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1024</t>
+  </si>
+  <si>
+    <t>11.7%</t>
+  </si>
+  <si>
     <t>10.6%</t>
   </si>
   <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
   </si>
   <si>
     <t>9.6%</t>
   </si>
   <si>
-    <t>8.5%</t>
+    <t>9.4%</t>
   </si>
   <si>
     <t>8.4%</t>
   </si>
   <si>
-    <t>+793</t>
-  </si>
-  <si>
-    <t>+801</t>
-  </si>
-  <si>
-    <t>+809</t>
+    <t>+755</t>
   </si>
   <si>
     <t>+843</t>
   </si>
   <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+920</t>
+    <t>+852</t>
+  </si>
+  <si>
+    <t>+931</t>
   </si>
   <si>
     <t>+942</t>
   </si>
   <si>
-    <t>+1076</t>
+    <t>+964</t>
   </si>
   <si>
     <t>+1090</t>
-  </si>
-  <si>
-    <t>10.9%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>+817</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+964</t>
   </si>
 </sst>
 </file>
@@ -581,7 +599,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -595,7 +613,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -609,7 +627,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -623,7 +641,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -637,7 +655,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -651,7 +669,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -665,7 +683,7 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -679,7 +697,7 @@
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -693,7 +711,7 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -704,10 +722,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -728,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -736,114 +754,114 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -854,24 +872,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -892,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -906,10 +924,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -934,10 +952,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -948,24 +966,24 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -976,66 +994,66 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t>Record</t>
   </si>
@@ -30,187 +30,193 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Mr Steinfeld's Stars</t>
+  </si>
+  <si>
+    <t>Division iPad</t>
+  </si>
+  <si>
+    <t>3rd World Immigrant</t>
+  </si>
+  <si>
     <t>Griddy Little Liars</t>
   </si>
   <si>
+    <t>I'm Batman</t>
+  </si>
+  <si>
+    <t>Michael, The Baker</t>
+  </si>
+  <si>
+    <t>Chicken Fried Chicken Meal</t>
+  </si>
+  <si>
+    <t>AJ's Awesome Team</t>
+  </si>
+  <si>
     <t>All my homies hate Dallas</t>
   </si>
   <si>
-    <t>Chicken Fried Chicken Meal</t>
-  </si>
-  <si>
-    <t>Division iPad</t>
-  </si>
-  <si>
-    <t>AJ's Awesome Team</t>
-  </si>
-  <si>
-    <t>Mr Steinfeld's Stars</t>
-  </si>
-  <si>
     <t>Scrappy Dub</t>
   </si>
   <si>
-    <t>3rd World Immigrant</t>
-  </si>
-  <si>
-    <t>Michael, The Baker</t>
-  </si>
-  <si>
-    <t>I'm Batman</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>62.9%</t>
-  </si>
-  <si>
-    <t>62.5%</t>
-  </si>
-  <si>
-    <t>62.3%</t>
-  </si>
-  <si>
-    <t>59.8%</t>
-  </si>
-  <si>
-    <t>59.4%</t>
+    <t>61.8%</t>
+  </si>
+  <si>
+    <t>61.3%</t>
+  </si>
+  <si>
+    <t>61.1%</t>
+  </si>
+  <si>
+    <t>61.0%</t>
+  </si>
+  <si>
+    <t>60.4%</t>
+  </si>
+  <si>
+    <t>60.3%</t>
+  </si>
+  <si>
+    <t>60.2%</t>
   </si>
   <si>
     <t>59.2%</t>
   </si>
   <si>
-    <t>59.1%</t>
-  </si>
-  <si>
-    <t>58.0%</t>
-  </si>
-  <si>
-    <t>57.0%</t>
-  </si>
-  <si>
-    <t>-170</t>
-  </si>
-  <si>
-    <t>-167</t>
-  </si>
-  <si>
-    <t>-165</t>
-  </si>
-  <si>
-    <t>-149</t>
-  </si>
-  <si>
-    <t>-146</t>
+    <t>58.7%</t>
+  </si>
+  <si>
+    <t>56.0%</t>
+  </si>
+  <si>
+    <t>-162</t>
+  </si>
+  <si>
+    <t>-158</t>
+  </si>
+  <si>
+    <t>-157</t>
+  </si>
+  <si>
+    <t>-156</t>
+  </si>
+  <si>
+    <t>-153</t>
+  </si>
+  <si>
+    <t>-152</t>
+  </si>
+  <si>
+    <t>-151</t>
   </si>
   <si>
     <t>-145</t>
   </si>
   <si>
-    <t>-144</t>
-  </si>
-  <si>
-    <t>-138</t>
-  </si>
-  <si>
-    <t>-133</t>
+    <t>-142</t>
+  </si>
+  <si>
+    <t>-127</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>11.3%</t>
+    <t>11.1%</t>
   </si>
   <si>
     <t>11.0%</t>
   </si>
   <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>9.5%</t>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>10.6%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>9.3%</t>
   </si>
   <si>
     <t>9.2%</t>
   </si>
   <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
-  </si>
-  <si>
-    <t>+785</t>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>+801</t>
   </si>
   <si>
     <t>+809</t>
   </si>
   <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+953</t>
+    <t>+835</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+862</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+975</t>
   </si>
   <si>
     <t>+987</t>
   </si>
   <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+1024</t>
-  </si>
-  <si>
-    <t>11.7%</t>
-  </si>
-  <si>
-    <t>10.6%</t>
+    <t>+1120</t>
+  </si>
+  <si>
+    <t>11.2%</t>
   </si>
   <si>
     <t>10.5%</t>
   </si>
   <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>9.9%</t>
+  </si>
+  <si>
     <t>9.7%</t>
   </si>
   <si>
     <t>9.6%</t>
   </si>
   <si>
-    <t>9.4%</t>
-  </si>
-  <si>
     <t>8.4%</t>
   </si>
   <si>
-    <t>+755</t>
-  </si>
-  <si>
-    <t>+843</t>
+    <t>+793</t>
   </si>
   <si>
     <t>+852</t>
   </si>
   <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+910</t>
+  </si>
+  <si>
     <t>+931</t>
   </si>
   <si>
     <t>+942</t>
-  </si>
-  <si>
-    <t>+964</t>
   </si>
   <si>
     <t>+1090</t>
@@ -599,7 +605,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -613,7 +619,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -627,7 +633,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -641,7 +647,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -652,10 +658,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -666,10 +672,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -680,10 +686,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -694,10 +700,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -708,10 +714,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -722,10 +728,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -754,16 +760,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -774,10 +780,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -788,10 +794,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -802,94 +808,94 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -910,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -924,136 +930,136 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
   <si>
     <t>Record</t>
   </si>
@@ -33,193 +33,181 @@
     <t>Mr Steinfeld's Stars</t>
   </si>
   <si>
+    <t>I'm Batman</t>
+  </si>
+  <si>
+    <t>Michael, The Baker</t>
+  </si>
+  <si>
+    <t>3rd World Immigrant</t>
+  </si>
+  <si>
+    <t>AJ's Awesome Team</t>
+  </si>
+  <si>
+    <t>Scrappy Dub</t>
+  </si>
+  <si>
+    <t>Chicken Fried Chicken Meal</t>
+  </si>
+  <si>
+    <t>Griddy Little Liars</t>
+  </si>
+  <si>
+    <t>All my homies hate Dallas</t>
+  </si>
+  <si>
     <t>Division iPad</t>
   </si>
   <si>
-    <t>3rd World Immigrant</t>
-  </si>
-  <si>
-    <t>Griddy Little Liars</t>
-  </si>
-  <si>
-    <t>I'm Batman</t>
-  </si>
-  <si>
-    <t>Michael, The Baker</t>
-  </si>
-  <si>
-    <t>Chicken Fried Chicken Meal</t>
-  </si>
-  <si>
-    <t>AJ's Awesome Team</t>
-  </si>
-  <si>
-    <t>All my homies hate Dallas</t>
-  </si>
-  <si>
-    <t>Scrappy Dub</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>61.8%</t>
-  </si>
-  <si>
-    <t>61.3%</t>
+    <t>62.2%</t>
   </si>
   <si>
     <t>61.1%</t>
   </si>
   <si>
-    <t>61.0%</t>
-  </si>
-  <si>
     <t>60.4%</t>
   </si>
   <si>
-    <t>60.3%</t>
-  </si>
-  <si>
     <t>60.2%</t>
   </si>
   <si>
+    <t>59.6%</t>
+  </si>
+  <si>
+    <t>59.5%</t>
+  </si>
+  <si>
     <t>59.2%</t>
   </si>
   <si>
-    <t>58.7%</t>
-  </si>
-  <si>
-    <t>56.0%</t>
-  </si>
-  <si>
-    <t>-162</t>
-  </si>
-  <si>
-    <t>-158</t>
+    <t>58.9%</t>
+  </si>
+  <si>
+    <t>58.5%</t>
+  </si>
+  <si>
+    <t>-165</t>
   </si>
   <si>
     <t>-157</t>
   </si>
   <si>
-    <t>-156</t>
-  </si>
-  <si>
     <t>-153</t>
   </si>
   <si>
-    <t>-152</t>
-  </si>
-  <si>
     <t>-151</t>
   </si>
   <si>
+    <t>-148</t>
+  </si>
+  <si>
+    <t>-147</t>
+  </si>
+  <si>
     <t>-145</t>
   </si>
   <si>
-    <t>-142</t>
-  </si>
-  <si>
-    <t>-127</t>
+    <t>-143</t>
+  </si>
+  <si>
+    <t>-141</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>11.1%</t>
-  </si>
-  <si>
     <t>11.0%</t>
   </si>
   <si>
-    <t>10.7%</t>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>8.8%</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+852</t>
+  </si>
+  <si>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+953</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1036</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
   </si>
   <si>
     <t>10.6%</t>
   </si>
   <si>
-    <t>10.4%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>9.3%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>8.2%</t>
-  </si>
-  <si>
-    <t>+801</t>
-  </si>
-  <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+835</t>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>8.7%</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+826</t>
   </si>
   <si>
     <t>+843</t>
   </si>
   <si>
-    <t>+862</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+975</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+1120</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>9.9%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
-  </si>
-  <si>
-    <t>+793</t>
-  </si>
-  <si>
-    <t>+852</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+910</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+1090</t>
+    <t>+900</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+1011</t>
+  </si>
+  <si>
+    <t>+1049</t>
   </si>
 </sst>
 </file>
@@ -605,7 +593,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -619,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -633,7 +621,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,10 +632,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -658,10 +646,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -672,10 +660,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -686,10 +674,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -700,10 +688,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -714,10 +702,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -728,10 +716,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -752,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -760,100 +748,100 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -864,10 +852,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -878,24 +866,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -916,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -924,16 +912,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -944,122 +932,122 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t>Record</t>
   </si>
@@ -30,121 +30,181 @@
     <t>Team</t>
   </si>
   <si>
+    <t>AJ's Awesome Team</t>
+  </si>
+  <si>
+    <t>Scrappy Dub</t>
+  </si>
+  <si>
+    <t>Chicken Fried Chicken Meal</t>
+  </si>
+  <si>
     <t>Mr Steinfeld's Stars</t>
   </si>
   <si>
     <t>I'm Batman</t>
   </si>
   <si>
+    <t>3rd World Immigrant</t>
+  </si>
+  <si>
+    <t>Division iPad</t>
+  </si>
+  <si>
+    <t>All my homies hate Dallas</t>
+  </si>
+  <si>
     <t>Michael, The Baker</t>
   </si>
   <si>
-    <t>3rd World Immigrant</t>
-  </si>
-  <si>
-    <t>AJ's Awesome Team</t>
-  </si>
-  <si>
-    <t>Scrappy Dub</t>
-  </si>
-  <si>
-    <t>Chicken Fried Chicken Meal</t>
-  </si>
-  <si>
     <t>Griddy Little Liars</t>
   </si>
   <si>
-    <t>All my homies hate Dallas</t>
-  </si>
-  <si>
-    <t>Division iPad</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>62.2%</t>
-  </si>
-  <si>
-    <t>61.1%</t>
+    <t>61.9%</t>
+  </si>
+  <si>
+    <t>61.7%</t>
+  </si>
+  <si>
+    <t>61.6%</t>
+  </si>
+  <si>
+    <t>60.7%</t>
   </si>
   <si>
     <t>60.4%</t>
   </si>
   <si>
-    <t>60.2%</t>
-  </si>
-  <si>
     <t>59.6%</t>
   </si>
   <si>
     <t>59.5%</t>
   </si>
   <si>
-    <t>59.2%</t>
-  </si>
-  <si>
-    <t>58.9%</t>
-  </si>
-  <si>
-    <t>58.5%</t>
-  </si>
-  <si>
-    <t>-165</t>
-  </si>
-  <si>
-    <t>-157</t>
+    <t>57.8%</t>
+  </si>
+  <si>
+    <t>57.2%</t>
+  </si>
+  <si>
+    <t>-162</t>
+  </si>
+  <si>
+    <t>-161</t>
+  </si>
+  <si>
+    <t>-160</t>
+  </si>
+  <si>
+    <t>-154</t>
   </si>
   <si>
     <t>-153</t>
   </si>
   <si>
-    <t>-151</t>
-  </si>
-  <si>
     <t>-148</t>
   </si>
   <si>
     <t>-147</t>
   </si>
   <si>
-    <t>-145</t>
-  </si>
-  <si>
-    <t>-143</t>
-  </si>
-  <si>
-    <t>-141</t>
+    <t>-137</t>
+  </si>
+  <si>
+    <t>-134</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
+    <t>12.2%</t>
+  </si>
+  <si>
     <t>11.0%</t>
   </si>
   <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>9.4%</t>
+  </si>
+  <si>
+    <t>8.8%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>+720</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+964</t>
+  </si>
+  <si>
+    <t>+1036</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>11.9%</t>
+  </si>
+  <si>
+    <t>10.6%</t>
+  </si>
+  <si>
     <t>10.5%</t>
   </si>
   <si>
     <t>10.2%</t>
   </si>
   <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>9.5%</t>
+    <t>9.2%</t>
   </si>
   <si>
     <t>9.1%</t>
   </si>
   <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>+809</t>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>+740</t>
+  </si>
+  <si>
+    <t>+843</t>
   </si>
   <si>
     <t>+852</t>
@@ -153,61 +213,13 @@
     <t>+880</t>
   </si>
   <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+953</t>
+    <t>+987</t>
   </si>
   <si>
     <t>+999</t>
   </si>
   <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>10.9%</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>10.6%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>9.0%</t>
-  </si>
-  <si>
-    <t>8.7%</t>
-  </si>
-  <si>
-    <t>+817</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+843</t>
-  </si>
-  <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+1011</t>
-  </si>
-  <si>
-    <t>+1049</t>
+    <t>+1090</t>
   </si>
 </sst>
 </file>
@@ -632,10 +644,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -646,10 +658,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -660,10 +672,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -748,7 +760,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -757,105 +769,105 @@
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -866,24 +878,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -912,114 +924,114 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1030,24 +1042,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
+++ b/data/odds/0755 Fantasy Football 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
   <si>
     <t>Record</t>
   </si>
@@ -30,64 +30,67 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Mr Steinfeld's Stars</t>
+  </si>
+  <si>
+    <t>All my homies hate Dallas</t>
+  </si>
+  <si>
+    <t>Michael, The Baker</t>
+  </si>
+  <si>
+    <t>Division iPad</t>
+  </si>
+  <si>
+    <t>Chicken Fried Chicken Meal</t>
+  </si>
+  <si>
+    <t>Scrappy Dub</t>
+  </si>
+  <si>
+    <t>I'm Batman</t>
+  </si>
+  <si>
     <t>AJ's Awesome Team</t>
   </si>
   <si>
-    <t>Scrappy Dub</t>
-  </si>
-  <si>
-    <t>Chicken Fried Chicken Meal</t>
-  </si>
-  <si>
-    <t>Mr Steinfeld's Stars</t>
-  </si>
-  <si>
-    <t>I'm Batman</t>
-  </si>
-  <si>
     <t>3rd World Immigrant</t>
   </si>
   <si>
-    <t>Division iPad</t>
-  </si>
-  <si>
-    <t>All my homies hate Dallas</t>
-  </si>
-  <si>
-    <t>Michael, The Baker</t>
-  </si>
-  <si>
     <t>Griddy Little Liars</t>
   </si>
   <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>61.9%</t>
+    <t>61.8%</t>
   </si>
   <si>
     <t>61.7%</t>
   </si>
   <si>
-    <t>61.6%</t>
-  </si>
-  <si>
-    <t>60.7%</t>
-  </si>
-  <si>
-    <t>60.4%</t>
-  </si>
-  <si>
-    <t>59.6%</t>
-  </si>
-  <si>
-    <t>59.5%</t>
-  </si>
-  <si>
-    <t>57.8%</t>
-  </si>
-  <si>
-    <t>57.2%</t>
+    <t>61.0%</t>
+  </si>
+  <si>
+    <t>60.9%</t>
+  </si>
+  <si>
+    <t>60.1%</t>
+  </si>
+  <si>
+    <t>59.3%</t>
+  </si>
+  <si>
+    <t>59.2%</t>
+  </si>
+  <si>
+    <t>58.9%</t>
+  </si>
+  <si>
+    <t>58.8%</t>
+  </si>
+  <si>
+    <t>58.3%</t>
   </si>
   <si>
     <t>-162</t>
@@ -96,130 +99,103 @@
     <t>-161</t>
   </si>
   <si>
-    <t>-160</t>
-  </si>
-  <si>
-    <t>-154</t>
-  </si>
-  <si>
-    <t>-153</t>
-  </si>
-  <si>
-    <t>-148</t>
-  </si>
-  <si>
-    <t>-147</t>
-  </si>
-  <si>
-    <t>-137</t>
-  </si>
-  <si>
-    <t>-134</t>
+    <t>-156</t>
+  </si>
+  <si>
+    <t>-151</t>
+  </si>
+  <si>
+    <t>-146</t>
+  </si>
+  <si>
+    <t>-145</t>
+  </si>
+  <si>
+    <t>-143</t>
+  </si>
+  <si>
+    <t>-140</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>12.2%</t>
-  </si>
-  <si>
-    <t>11.0%</t>
+    <t>11.5%</t>
+  </si>
+  <si>
+    <t>11.1%</t>
   </si>
   <si>
     <t>10.8%</t>
   </si>
   <si>
+    <t>10.6%</t>
+  </si>
+  <si>
     <t>10.1%</t>
   </si>
   <si>
-    <t>9.8%</t>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>+770</t>
+  </si>
+  <si>
+    <t>+801</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+1011</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>9.9%</t>
   </si>
   <si>
     <t>9.7%</t>
   </si>
   <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>8.6%</t>
-  </si>
-  <si>
-    <t>+720</t>
-  </si>
-  <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+920</t>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+910</t>
   </si>
   <si>
     <t>+931</t>
   </si>
   <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+964</t>
-  </si>
-  <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>+1063</t>
-  </si>
-  <si>
-    <t>11.9%</t>
-  </si>
-  <si>
-    <t>10.6%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
-  </si>
-  <si>
-    <t>+740</t>
-  </si>
-  <si>
-    <t>+843</t>
-  </si>
-  <si>
-    <t>+852</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+1090</t>
+    <t>+953</t>
   </si>
 </sst>
 </file>
@@ -605,7 +581,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -619,7 +595,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -633,7 +609,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -686,10 +662,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -700,10 +676,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -714,7 +690,7 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -728,7 +704,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -760,7 +736,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -769,7 +745,7 @@
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -783,12 +759,12 @@
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -797,12 +773,12 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -811,12 +787,12 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -825,7 +801,7 @@
         <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -839,35 +815,35 @@
         <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -878,24 +854,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -924,58 +900,58 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -986,80 +962,80 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
         <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
